--- a/salidas/empresas/EOG.xlsx
+++ b/salidas/empresas/EOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.69246864318848</v>
+        <v>28.69247436523438</v>
       </c>
       <c r="C2" t="n">
         <v>42.27000045776367</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.8752326965332</v>
+        <v>22.87523651123047</v>
       </c>
       <c r="C3" t="n">
         <v>33.70000076293945</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.43645095825195</v>
+        <v>24.43644332885742</v>
       </c>
       <c r="C4" t="n">
         <v>36</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.30279922485352</v>
+        <v>22.30279159545898</v>
       </c>
       <c r="C6" t="n">
         <v>32.83000183105469</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>23.55277633666992</v>
+        <v>23.55278205871582</v>
       </c>
       <c r="C7" t="n">
         <v>34.66999816894531</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>25.20813941955566</v>
+        <v>25.20812606811523</v>
       </c>
       <c r="C8" t="n">
         <v>37.07500076293945</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.03629302978516</v>
+        <v>22.03629875183105</v>
       </c>
       <c r="C9" t="n">
         <v>32.40999984741211</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>22.11448287963867</v>
+        <v>22.11448860168457</v>
       </c>
       <c r="C10" t="n">
         <v>32.52500152587891</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>24.00007629394531</v>
+        <v>24.00007057189941</v>
       </c>
       <c r="C12" t="n">
         <v>35.26499938964844</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>21.25060272216797</v>
+        <v>21.2505989074707</v>
       </c>
       <c r="C13" t="n">
         <v>31.22500038146973</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.5472469329834</v>
+        <v>23.54723930358887</v>
       </c>
       <c r="C14" t="n">
         <v>34.56499862670898</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>23.07377433776855</v>
+        <v>23.07378196716309</v>
       </c>
       <c r="C15" t="n">
         <v>33.86999893188477</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>24.30000686645508</v>
+        <v>24.30000877380371</v>
       </c>
       <c r="C16" t="n">
         <v>35.66999816894531</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>25.04529762268066</v>
+        <v>25.04529190063477</v>
       </c>
       <c r="C17" t="n">
         <v>36.72000122070312</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.22526168823242</v>
+        <v>26.22526359558105</v>
       </c>
       <c r="C18" t="n">
         <v>38.45000076293945</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.91570472717285</v>
+        <v>24.91569519042969</v>
       </c>
       <c r="C19" t="n">
         <v>36.52999877929688</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>22.99957084655762</v>
+        <v>22.99957656860352</v>
       </c>
       <c r="C21" t="n">
         <v>33.68000030517578</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>30.28531837463379</v>
+        <v>30.28530693054199</v>
       </c>
       <c r="C23" t="n">
         <v>44.29999923706055</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>28.29592514038086</v>
+        <v>28.29591751098633</v>
       </c>
       <c r="C24" t="n">
         <v>41.38999938964844</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>30.50751304626465</v>
+        <v>30.50750160217285</v>
       </c>
       <c r="C25" t="n">
         <v>44.625</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.88007736206055</v>
+        <v>29.88007164001465</v>
       </c>
       <c r="C26" t="n">
         <v>43.66500091552734</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>40.71257400512695</v>
+        <v>40.71258544921875</v>
       </c>
       <c r="C27" t="n">
         <v>59.49499893188477</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>44.68633270263672</v>
+        <v>44.68634796142578</v>
       </c>
       <c r="C29" t="n">
         <v>65.23999786376953</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>44.05275726318359</v>
+        <v>44.05277252197266</v>
       </c>
       <c r="C30" t="n">
         <v>64.31500244140625</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>44.93291473388672</v>
+        <v>44.93292617797852</v>
       </c>
       <c r="C31" t="n">
         <v>65.59999847412109</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.46390914916992</v>
+        <v>34.46392059326172</v>
       </c>
       <c r="C32" t="n">
         <v>50.26499938964844</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>30.66887474060059</v>
+        <v>30.66888809204102</v>
       </c>
       <c r="C34" t="n">
         <v>44.72999954223633</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>27.7940731048584</v>
+        <v>27.7940616607666</v>
       </c>
       <c r="C35" t="n">
         <v>40.45999908447266</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>29.20231628417969</v>
+        <v>29.20232009887695</v>
       </c>
       <c r="C36" t="n">
         <v>42.5099983215332</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>23.32430267333984</v>
+        <v>23.32429504394531</v>
       </c>
       <c r="C38" t="n">
         <v>33.8849983215332</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.22219848632812</v>
+        <v>17.22219657897949</v>
       </c>
       <c r="C39" t="n">
         <v>25.02000045776367</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.84665870666504</v>
+        <v>18.84666061401367</v>
       </c>
       <c r="C40" t="n">
         <v>27.3799991607666</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>25.2487678527832</v>
+        <v>25.24877738952637</v>
       </c>
       <c r="C42" t="n">
         <v>36.59500122070312</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>23.43074798583984</v>
+        <v>23.43075180053711</v>
       </c>
       <c r="C43" t="n">
         <v>33.95999908447266</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.59593963623047</v>
+        <v>25.59593391418457</v>
       </c>
       <c r="C44" t="n">
         <v>37.01499938964844</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.89406585693359</v>
+        <v>24.89406967163086</v>
       </c>
       <c r="C45" t="n">
         <v>36</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>28.8736629486084</v>
+        <v>28.87365341186523</v>
       </c>
       <c r="C46" t="n">
         <v>41.75500106811523</v>
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.95245933532715</v>
+        <v>29.95246124267578</v>
       </c>
       <c r="C48" t="n">
         <v>43.24499893188477</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.69607162475586</v>
+        <v>33.69609451293945</v>
       </c>
       <c r="C49" t="n">
         <v>48.65000152587891</v>
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>31.36111640930176</v>
+        <v>31.36110496520996</v>
       </c>
       <c r="C50" t="n">
         <v>45.20999908447266</v>
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>32.62013244628906</v>
+        <v>32.62013626098633</v>
       </c>
       <c r="C51" t="n">
         <v>47.02500152587891</v>
@@ -1456,11 +1468,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.23513031005859</v>
+        <v>32.23514938354492</v>
       </c>
       <c r="C52" t="n">
         <v>46.47000122070312</v>
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.94371795654297</v>
+        <v>38.94371032714844</v>
       </c>
       <c r="C53" t="n">
         <v>56.06000137329102</v>
@@ -1506,7 +1518,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1531,7 +1543,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>33.91483306884766</v>
+        <v>33.91481781005859</v>
       </c>
       <c r="C56" t="n">
         <v>48.75</v>
@@ -1581,11 +1593,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>30.21725082397461</v>
+        <v>30.21723937988281</v>
       </c>
       <c r="C57" t="n">
         <v>43.43500137329102</v>
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>32.33907318115234</v>
+        <v>32.3390998840332</v>
       </c>
       <c r="C58" t="n">
         <v>46.48500061035156</v>
@@ -1631,11 +1643,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.34791564941406</v>
+        <v>33.34792709350586</v>
       </c>
       <c r="C59" t="n">
         <v>47.86000061035156</v>
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>30.98932075500488</v>
+        <v>30.98931503295898</v>
       </c>
       <c r="C60" t="n">
         <v>44.47499847412109</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>31.84635734558105</v>
+        <v>31.84634971618652</v>
       </c>
       <c r="C61" t="n">
         <v>45.70500183105469</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>37.12474822998047</v>
+        <v>37.1247444152832</v>
       </c>
       <c r="C62" t="n">
         <v>53.19499969482422</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.19051361083984</v>
+        <v>39.19051742553711</v>
       </c>
       <c r="C63" t="n">
         <v>56.15499877929688</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>41.35400009155273</v>
+        <v>41.35400390625</v>
       </c>
       <c r="C64" t="n">
         <v>59.25500106811523</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.50661849975586</v>
+        <v>39.5066032409668</v>
       </c>
       <c r="C65" t="n">
         <v>56.52500152587891</v>
@@ -1818,7 +1830,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1847,11 +1859,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>36.53619384765625</v>
+        <v>36.53619003295898</v>
       </c>
       <c r="C67" t="n">
         <v>52.27500152587891</v>
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>35.70283889770508</v>
+        <v>35.70281219482422</v>
       </c>
       <c r="C68" t="n">
         <v>51</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>32.40906524658203</v>
+        <v>32.40907287597656</v>
       </c>
       <c r="C69" t="n">
         <v>46.29499816894531</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>24.85546684265137</v>
+        <v>24.8554744720459</v>
       </c>
       <c r="C70" t="n">
         <v>35.50500106811523</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>31.36498641967773</v>
+        <v>31.36498260498047</v>
       </c>
       <c r="C71" t="n">
         <v>44.71500015258789</v>
@@ -1992,7 +2004,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>34.54951858520508</v>
+        <v>34.54952239990234</v>
       </c>
       <c r="C73" t="n">
         <v>49.25500106811523</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>37.28334808349609</v>
+        <v>37.28334045410156</v>
       </c>
       <c r="C74" t="n">
         <v>53.06999969482422</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>39.99512100219727</v>
+        <v>39.9951171875</v>
       </c>
       <c r="C75" t="n">
         <v>56.93000030517578</v>
@@ -2108,11 +2120,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>39.02563095092773</v>
+        <v>39.02560806274414</v>
       </c>
       <c r="C76" t="n">
         <v>55.54999923706055</v>
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>38.63629150390625</v>
+        <v>38.63628768920898</v>
       </c>
       <c r="C77" t="n">
         <v>54.90499877929688</v>
@@ -2166,11 +2178,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>34.93838882446289</v>
+        <v>34.93838500976562</v>
       </c>
       <c r="C78" t="n">
         <v>49.65000152587891</v>
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>31.70490837097168</v>
+        <v>31.70489883422852</v>
       </c>
       <c r="C79" t="n">
         <v>45.05500030517578</v>
@@ -2224,7 +2236,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2253,11 +2265,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>38.17629623413086</v>
+        <v>38.17627334594727</v>
       </c>
       <c r="C81" t="n">
         <v>54.15000152587891</v>
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>39.49817657470703</v>
+        <v>39.4981689453125</v>
       </c>
       <c r="C82" t="n">
         <v>56.02500152587891</v>
@@ -2311,11 +2323,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>41.1275749206543</v>
+        <v>41.1275634765625</v>
       </c>
       <c r="C83" t="n">
         <v>58.24499893188477</v>
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>41.52652740478516</v>
+        <v>41.52651214599609</v>
       </c>
       <c r="C84" t="n">
         <v>58.81000137329102</v>
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.64572525024414</v>
+        <v>42.64572143554688</v>
       </c>
       <c r="C85" t="n">
         <v>60.39500045776367</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>44.18526458740234</v>
+        <v>44.18526077270508</v>
       </c>
       <c r="C86" t="n">
         <v>62.4900016784668</v>
@@ -2427,7 +2439,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>45.27770233154297</v>
+        <v>45.27771759033203</v>
       </c>
       <c r="C88" t="n">
         <v>64.03500366210938</v>
@@ -2485,11 +2497,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.89762878417969</v>
+        <v>42.89761734008789</v>
       </c>
       <c r="C89" t="n">
         <v>60.58000183105469</v>
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>45.7088508605957</v>
+        <v>45.70885467529297</v>
       </c>
       <c r="C90" t="n">
         <v>64.55000305175781</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>46.62230682373047</v>
+        <v>46.622314453125</v>
       </c>
       <c r="C91" t="n">
         <v>65.83999633789062</v>
@@ -2572,11 +2584,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>51.57885360717773</v>
+        <v>51.57887268066406</v>
       </c>
       <c r="C92" t="n">
         <v>72.74500274658203</v>
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>55.67707061767578</v>
+        <v>55.67710876464844</v>
       </c>
       <c r="C93" t="n">
         <v>78.52500152587891</v>
@@ -2630,11 +2642,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>60.01283645629883</v>
+        <v>60.01288223266602</v>
       </c>
       <c r="C94" t="n">
         <v>84.63999938964844</v>
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>63.31177139282227</v>
+        <v>63.31178665161133</v>
       </c>
       <c r="C95" t="n">
         <v>89.19999694824219</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>58.55631256103516</v>
+        <v>58.55631637573242</v>
       </c>
       <c r="C96" t="n">
         <v>82.5</v>
@@ -2717,11 +2729,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>59.56418991088867</v>
+        <v>59.564208984375</v>
       </c>
       <c r="C97" t="n">
         <v>83.91999816894531</v>
@@ -2746,11 +2758,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>58.70694732666016</v>
+        <v>58.70695877075195</v>
       </c>
       <c r="C98" t="n">
         <v>82.62000274658203</v>
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>67.29769134521484</v>
+        <v>67.29767608642578</v>
       </c>
       <c r="C99" t="n">
         <v>94.70999908447266</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>69.69583892822266</v>
+        <v>69.69583129882812</v>
       </c>
       <c r="C100" t="n">
         <v>98.08499908447266</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>69.72381591796875</v>
+        <v>69.72384643554688</v>
       </c>
       <c r="C101" t="n">
         <v>98</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>75.27328491210938</v>
+        <v>75.27323150634766</v>
       </c>
       <c r="C102" t="n">
         <v>105.8000030517578</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>83.14209747314453</v>
+        <v>83.14208221435547</v>
       </c>
       <c r="C103" t="n">
         <v>116.8600006103516</v>
@@ -2920,11 +2932,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>77.94721984863281</v>
+        <v>77.94725036621094</v>
       </c>
       <c r="C104" t="n">
         <v>109.4400024414062</v>
@@ -2949,11 +2961,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>78.2606201171875</v>
+        <v>78.26058959960938</v>
       </c>
       <c r="C105" t="n">
         <v>109.879997253418</v>
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.52571868896484</v>
+        <v>70.52570343017578</v>
       </c>
       <c r="C106" t="n">
         <v>99.01999664306641</v>
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>67.83406066894531</v>
+        <v>67.83404541015625</v>
       </c>
       <c r="C107" t="n">
         <v>95.05000305175781</v>
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>61.88922119140625</v>
+        <v>61.88919830322266</v>
       </c>
       <c r="C108" t="n">
         <v>86.72000122070312</v>
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>65.70732879638672</v>
+        <v>65.70736694335938</v>
       </c>
       <c r="C109" t="n">
         <v>92.06999969482422</v>
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>63.66353225708008</v>
+        <v>63.66349411010742</v>
       </c>
       <c r="C110" t="n">
         <v>89.02999877929688</v>
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>64.15693664550781</v>
+        <v>64.15692901611328</v>
       </c>
       <c r="C111" t="n">
         <v>89.72000122070312</v>
@@ -3152,11 +3164,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>65.56565093994141</v>
+        <v>65.56561279296875</v>
       </c>
       <c r="C112" t="n">
         <v>91.69000244140625</v>
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>70.88285827636719</v>
+        <v>70.88288116455078</v>
       </c>
       <c r="C113" t="n">
         <v>98.94999694824219</v>
@@ -3210,7 +3222,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3239,7 +3251,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>55.40429306030273</v>
+        <v>55.4043083190918</v>
       </c>
       <c r="C116" t="n">
         <v>77.19000244140625</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>56.20820236206055</v>
+        <v>56.20817947387695</v>
       </c>
       <c r="C117" t="n">
         <v>78.30999755859375</v>
@@ -3326,11 +3338,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>52.2532958984375</v>
+        <v>52.2533073425293</v>
       </c>
       <c r="C118" t="n">
         <v>72.80000305175781</v>
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>61.74178314208984</v>
+        <v>61.74177169799805</v>
       </c>
       <c r="C119" t="n">
         <v>85.84999847412109</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>60.00138473510742</v>
+        <v>60.00134658813477</v>
       </c>
       <c r="C120" t="n">
         <v>83.43000030517578</v>
@@ -3411,7 +3423,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3438,11 +3450,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>51.21304321289062</v>
+        <v>51.21305084228516</v>
       </c>
       <c r="C122" t="n">
         <v>71.01999664306641</v>
@@ -3465,11 +3477,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>46.68447113037109</v>
+        <v>46.68449020385742</v>
       </c>
       <c r="C123" t="n">
         <v>64.73999786376953</v>
@@ -3492,11 +3504,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>52.33796691894531</v>
+        <v>52.33797836303711</v>
       </c>
       <c r="C124" t="n">
         <v>72.58000183105469</v>
@@ -3519,11 +3531,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>59.70732879638672</v>
+        <v>59.70731353759766</v>
       </c>
       <c r="C125" t="n">
         <v>82.62000274658203</v>
@@ -3546,11 +3558,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>58.79673004150391</v>
+        <v>58.79672241210938</v>
       </c>
       <c r="C126" t="n">
         <v>81.36000061035156</v>
@@ -3573,11 +3585,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.28542327880859</v>
+        <v>60.28545379638672</v>
       </c>
       <c r="C127" t="n">
         <v>83.41999816894531</v>
@@ -3600,11 +3612,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>59.15916061401367</v>
+        <v>59.15918350219727</v>
       </c>
       <c r="C128" t="n">
         <v>81.69999694824219</v>
@@ -3627,7 +3639,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3654,11 +3666,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>70.02794647216797</v>
+        <v>70.02797698974609</v>
       </c>
       <c r="C130" t="n">
         <v>96.70999908447266</v>
@@ -3681,7 +3693,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3708,11 +3720,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>74.36473846435547</v>
+        <v>74.36473083496094</v>
       </c>
       <c r="C132" t="n">
         <v>102.5199966430664</v>
@@ -3735,11 +3747,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>73.33470153808594</v>
+        <v>73.334716796875</v>
       </c>
       <c r="C133" t="n">
         <v>101.0999984741211</v>
@@ -3762,11 +3774,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>73.80104064941406</v>
+        <v>73.80104827880859</v>
       </c>
       <c r="C134" t="n">
         <v>101.5800018310547</v>
@@ -3789,7 +3801,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3816,11 +3828,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>70.87312316894531</v>
+        <v>70.87313079833984</v>
       </c>
       <c r="C136" t="n">
         <v>97.55000305175781</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>67.31887054443359</v>
+        <v>67.31888580322266</v>
       </c>
       <c r="C137" t="n">
         <v>92.5</v>
@@ -3870,7 +3882,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3897,11 +3909,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>65.87789154052734</v>
+        <v>65.87789916992188</v>
       </c>
       <c r="C139" t="n">
         <v>90.51999664306641</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>69.36888885498047</v>
+        <v>69.36887359619141</v>
       </c>
       <c r="C140" t="n">
         <v>95.13999938964844</v>
@@ -3951,11 +3963,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>61.9682731628418</v>
+        <v>61.96826171875</v>
       </c>
       <c r="C141" t="n">
         <v>84.98999786376953</v>
@@ -3978,11 +3990,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>70.53547668457031</v>
+        <v>70.53546142578125</v>
       </c>
       <c r="C142" t="n">
         <v>96.73999786376953</v>
@@ -4005,11 +4017,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>72.94448089599609</v>
+        <v>72.9444580078125</v>
       </c>
       <c r="C143" t="n">
         <v>99.87000274658203</v>
@@ -4032,11 +4044,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>74.73394012451172</v>
+        <v>74.73393249511719</v>
       </c>
       <c r="C144" t="n">
         <v>102.3199996948242</v>
@@ -4061,11 +4073,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.81683349609375</v>
+        <v>78.81684112548828</v>
       </c>
       <c r="C145" t="n">
         <v>107.9100036621094</v>
@@ -4090,11 +4102,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>84.11746215820312</v>
+        <v>84.11748504638672</v>
       </c>
       <c r="C146" t="n">
         <v>115</v>
@@ -4119,11 +4131,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>74.18428039550781</v>
+        <v>74.18430328369141</v>
       </c>
       <c r="C147" t="n">
         <v>101.4199981689453</v>
@@ -4148,7 +4160,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4177,11 +4189,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>86.58181762695312</v>
+        <v>86.58183288574219</v>
       </c>
       <c r="C149" t="n">
         <v>118.1699981689453</v>
@@ -4206,11 +4218,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>86.31806182861328</v>
+        <v>86.31807708740234</v>
       </c>
       <c r="C150" t="n">
         <v>117.8099975585938</v>
@@ -4235,11 +4247,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>91.16845703125</v>
+        <v>91.16844177246094</v>
       </c>
       <c r="C151" t="n">
         <v>124.4300003051758</v>
@@ -4264,11 +4276,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>94.61184692382812</v>
+        <v>94.61185455322266</v>
       </c>
       <c r="C152" t="n">
         <v>128.9400024414062</v>
@@ -4293,7 +4305,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4322,11 +4334,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>93.60658264160156</v>
+        <v>93.60659790039062</v>
       </c>
       <c r="C154" t="n">
         <v>127.5699996948242</v>
@@ -4351,7 +4363,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4380,11 +4392,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>75.94170379638672</v>
+        <v>75.94171905517578</v>
       </c>
       <c r="C156" t="n">
         <v>103.3099975585938</v>
@@ -4409,7 +4421,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4438,11 +4450,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>73.08359527587891</v>
+        <v>73.08361053466797</v>
       </c>
       <c r="C158" t="n">
         <v>99.19999694824219</v>
@@ -4467,11 +4479,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>69.25260925292969</v>
+        <v>69.25260162353516</v>
       </c>
       <c r="C159" t="n">
         <v>94</v>
@@ -4496,11 +4508,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>70.12194061279297</v>
+        <v>70.12195587158203</v>
       </c>
       <c r="C160" t="n">
         <v>95.18000030517578</v>
@@ -4525,11 +4537,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>70.91103363037109</v>
+        <v>70.91104125976562</v>
       </c>
       <c r="C161" t="n">
         <v>96.05000305175781</v>
@@ -4554,11 +4566,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>60.44971084594727</v>
+        <v>60.44973754882812</v>
       </c>
       <c r="C162" t="n">
         <v>81.87999725341797</v>
@@ -4583,11 +4595,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>68.77744293212891</v>
+        <v>68.77745056152344</v>
       </c>
       <c r="C163" t="n">
         <v>93.16000366210938</v>
@@ -4612,11 +4624,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>63.58701705932617</v>
+        <v>63.58700180053711</v>
       </c>
       <c r="C164" t="n">
         <v>85.84999847412109</v>
@@ -4641,7 +4653,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4670,11 +4682,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>54.97295761108398</v>
+        <v>54.97293853759766</v>
       </c>
       <c r="C166" t="n">
         <v>74.22000122070312</v>
@@ -4699,11 +4711,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>51.55062866210938</v>
+        <v>51.55062103271484</v>
       </c>
       <c r="C167" t="n">
         <v>69.30999755859375</v>
@@ -4728,11 +4740,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>52.73323059082031</v>
+        <v>52.73322677612305</v>
       </c>
       <c r="C168" t="n">
         <v>70.90000152587891</v>
@@ -4757,11 +4769,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>62.29808807373047</v>
+        <v>62.2980842590332</v>
       </c>
       <c r="C169" t="n">
         <v>83.76000213623047</v>
@@ -4786,7 +4798,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4815,11 +4827,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.20756912231445</v>
+        <v>47.20756149291992</v>
       </c>
       <c r="C171" t="n">
         <v>63.2599983215332</v>
@@ -4844,11 +4856,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>26.8051815032959</v>
+        <v>26.80517959594727</v>
       </c>
       <c r="C172" t="n">
         <v>35.91999816894531</v>
@@ -4873,11 +4885,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>35.77182769775391</v>
+        <v>35.77183532714844</v>
       </c>
       <c r="C173" t="n">
         <v>47.5099983215332</v>
@@ -4902,11 +4914,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.37697982788086</v>
+        <v>38.37697601318359</v>
       </c>
       <c r="C174" t="n">
         <v>50.97000122070312</v>
@@ -4931,11 +4943,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>38.1435661315918</v>
+        <v>38.14356994628906</v>
       </c>
       <c r="C175" t="n">
         <v>50.65999984741211</v>
@@ -4960,11 +4972,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>35.55583190917969</v>
+        <v>35.55582809448242</v>
       </c>
       <c r="C176" t="n">
         <v>46.84999847412109</v>
@@ -4989,7 +5001,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5018,11 +5030,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>27.27591705322266</v>
+        <v>27.27591896057129</v>
       </c>
       <c r="C178" t="n">
         <v>35.93999862670898</v>
@@ -5047,11 +5059,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>26.24737167358398</v>
+        <v>26.24737548828125</v>
       </c>
       <c r="C179" t="n">
         <v>34.2400016784668</v>
@@ -5076,11 +5088,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>35.93682098388672</v>
+        <v>35.93682861328125</v>
       </c>
       <c r="C180" t="n">
         <v>46.88000106811523</v>
@@ -5103,11 +5115,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>38.22885513305664</v>
+        <v>38.2288703918457</v>
       </c>
       <c r="C181" t="n">
         <v>49.86999893188477</v>
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>39.30820846557617</v>
+        <v>39.30820465087891</v>
       </c>
       <c r="C182" t="n">
         <v>50.95999908447266</v>
@@ -5157,11 +5169,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>49.79860687255859</v>
+        <v>49.79861068725586</v>
       </c>
       <c r="C183" t="n">
         <v>64.55999755859375</v>
@@ -5184,11 +5196,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>55.94630813598633</v>
+        <v>55.94631195068359</v>
       </c>
       <c r="C184" t="n">
         <v>72.52999877929688</v>
@@ -5211,11 +5223,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>57.12079238891602</v>
+        <v>57.12077331542969</v>
       </c>
       <c r="C185" t="n">
         <v>73.63999938964844</v>
@@ -5238,11 +5250,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>62.31782531738281</v>
+        <v>62.31781387329102</v>
       </c>
       <c r="C186" t="n">
         <v>80.33999633789062</v>
@@ -5267,11 +5279,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>64.72240447998047</v>
+        <v>64.72241973876953</v>
       </c>
       <c r="C187" t="n">
         <v>83.44000244140625</v>
@@ -5296,11 +5308,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>57.53631591796875</v>
+        <v>57.53632736206055</v>
       </c>
       <c r="C188" t="n">
         <v>72.86000061035156</v>
@@ -5325,11 +5337,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>53.31943130493164</v>
+        <v>53.31941223144531</v>
       </c>
       <c r="C189" t="n">
         <v>67.51999664306641</v>
@@ -5354,11 +5366,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>63.38789367675781</v>
+        <v>63.38788604736328</v>
       </c>
       <c r="C190" t="n">
         <v>80.26999664306641</v>
@@ -5383,11 +5395,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>73.34917449951172</v>
+        <v>73.34921264648438</v>
       </c>
       <c r="C191" t="n">
         <v>92.45999908447266</v>
@@ -5412,11 +5424,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>69.01773071289062</v>
+        <v>69.0177001953125</v>
       </c>
       <c r="C192" t="n">
         <v>87</v>
@@ -5441,11 +5453,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>72.10774230957031</v>
+        <v>72.10775756835938</v>
       </c>
       <c r="C193" t="n">
         <v>88.83000183105469</v>
@@ -5470,11 +5482,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>91.15915679931641</v>
+        <v>91.15914154052734</v>
       </c>
       <c r="C194" t="n">
         <v>111.4800033569336</v>
@@ -5499,11 +5511,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>93.97208404541016</v>
+        <v>93.97209167480469</v>
       </c>
       <c r="C195" t="n">
         <v>114.9199981689453</v>
@@ -5528,7 +5540,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5557,11 +5569,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>96.88536071777344</v>
+        <v>96.88535308837891</v>
       </c>
       <c r="C197" t="n">
         <v>116.7600021362305</v>
@@ -5586,11 +5598,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>113.6469573974609</v>
+        <v>113.64697265625</v>
       </c>
       <c r="C198" t="n">
         <v>136.9600067138672</v>
@@ -5615,7 +5627,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5644,11 +5656,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>94.26847839355469</v>
+        <v>94.26848602294922</v>
       </c>
       <c r="C200" t="n">
         <v>111.2200012207031</v>
@@ -5673,11 +5685,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>102.8121490478516</v>
+        <v>102.8121337890625</v>
       </c>
       <c r="C201" t="n">
         <v>121.3000030517578</v>
@@ -5702,11 +5714,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>95.87076568603516</v>
+        <v>95.87075805664062</v>
       </c>
       <c r="C202" t="n">
         <v>111.7300033569336</v>
@@ -5731,11 +5743,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>117.8360366821289</v>
+        <v>117.8360443115234</v>
       </c>
       <c r="C203" t="n">
         <v>136.5200042724609</v>
@@ -5760,11 +5772,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>122.5056304931641</v>
+        <v>122.5055999755859</v>
       </c>
       <c r="C204" t="n">
         <v>141.9299926757812</v>
@@ -5789,11 +5801,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>113.1253509521484</v>
+        <v>113.1253356933594</v>
       </c>
       <c r="C205" t="n">
         <v>129.5200042724609</v>
@@ -5818,11 +5830,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>116.2449417114258</v>
+        <v>116.2449493408203</v>
       </c>
       <c r="C206" t="n">
         <v>132.25</v>
@@ -5847,11 +5859,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>99.34217834472656</v>
+        <v>99.34218597412109</v>
       </c>
       <c r="C207" t="n">
         <v>113.0199966430664</v>
@@ -5876,11 +5888,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>101.6885528564453</v>
+        <v>101.6885604858398</v>
       </c>
       <c r="C208" t="n">
         <v>114.629997253418</v>
@@ -5905,11 +5917,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>106.7018432617188</v>
+        <v>106.7018508911133</v>
       </c>
       <c r="C209" t="n">
         <v>119.4700012207031</v>
@@ -5934,11 +5946,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>95.82357025146484</v>
+        <v>95.82357788085938</v>
       </c>
       <c r="C210" t="n">
         <v>107.2900009155273</v>
@@ -5963,11 +5975,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>102.2094497680664</v>
+        <v>102.2094268798828</v>
       </c>
       <c r="C211" t="n">
         <v>114.4400024414062</v>
@@ -5992,11 +6004,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>119.1682052612305</v>
+        <v>119.1681976318359</v>
       </c>
       <c r="C212" t="n">
         <v>132.5299987792969</v>
@@ -6021,11 +6033,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>115.6523971557617</v>
+        <v>115.6524047851562</v>
       </c>
       <c r="C213" t="n">
         <v>128.6199951171875</v>
@@ -6050,11 +6062,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>113.9799346923828</v>
+        <v>113.9799499511719</v>
       </c>
       <c r="C214" t="n">
         <v>126.7600021362305</v>
@@ -6079,7 +6091,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6108,7 +6120,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6137,11 +6149,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>110.8334274291992</v>
+        <v>110.8334350585938</v>
       </c>
       <c r="C217" t="n">
         <v>120.9499969482422</v>
@@ -6166,7 +6178,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6195,7 +6207,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6224,11 +6236,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>118.072998046875</v>
+        <v>118.0729904174805</v>
       </c>
       <c r="C220" t="n">
         <v>127.8399963378906</v>
@@ -6253,11 +6265,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>122.8616638183594</v>
+        <v>122.8616561889648</v>
       </c>
       <c r="C221" t="n">
         <v>132.1300048828125</v>
@@ -6282,11 +6294,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>115.813346862793</v>
+        <v>115.8133697509766</v>
       </c>
       <c r="C222" t="n">
         <v>124.5500030517578</v>
@@ -6311,11 +6323,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>117.0407638549805</v>
+        <v>117.0407562255859</v>
       </c>
       <c r="C223" t="n">
         <v>125.870002746582</v>
@@ -6340,7 +6352,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6369,11 +6381,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>120.618408203125</v>
+        <v>120.6184158325195</v>
       </c>
       <c r="C225" t="n">
         <v>128.8200073242188</v>
@@ -6398,7 +6410,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6427,7 +6439,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6456,11 +6468,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>125.6736602783203</v>
+        <v>125.6736755371094</v>
       </c>
       <c r="C228" t="n">
         <v>133.2599945068359</v>
@@ -6485,11 +6497,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>115.6016616821289</v>
+        <v>115.6016693115234</v>
       </c>
       <c r="C229" t="n">
         <v>122.5800018310547</v>
@@ -6514,11 +6526,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>119.4727172851562</v>
+        <v>119.4727249145508</v>
       </c>
       <c r="C230" t="n">
         <v>125.7900009155273</v>
@@ -6543,11 +6555,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>120.5649719238281</v>
+        <v>120.5649795532227</v>
       </c>
       <c r="C231" t="n">
         <v>126.9400024414062</v>
@@ -6572,7 +6584,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6601,7 +6613,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6630,7 +6642,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6659,11 +6671,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>114.6430740356445</v>
+        <v>114.64306640625</v>
       </c>
       <c r="C235" t="n">
         <v>119.6100006103516</v>
@@ -6688,11 +6700,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>115.9879608154297</v>
+        <v>115.9879531860352</v>
       </c>
       <c r="C236" t="n">
         <v>120.0199966430664</v>
@@ -6717,11 +6729,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>120.6267166137695</v>
+        <v>120.626708984375</v>
       </c>
       <c r="C237" t="n">
         <v>124.8199996948242</v>
@@ -6746,7 +6758,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6775,7 +6787,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6804,7 +6816,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6833,7 +6845,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6862,7 +6874,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6891,7 +6903,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6920,7 +6932,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6949,7 +6961,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6978,7 +6990,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7007,7 +7019,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7036,7 +7048,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7065,7 +7077,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7094,32 +7106,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>141.8399963378906</v>
+        <v>142.8600006103516</v>
       </c>
       <c r="C250" t="n">
-        <v>141.8399963378906</v>
+        <v>142.8600006103516</v>
       </c>
       <c r="D250" t="n">
-        <v>56334000</v>
+        <v>59006000</v>
       </c>
       <c r="E250" t="n">
         <v>12.86</v>
       </c>
       <c r="F250" t="n">
-        <v>11.02954870434608</v>
+        <v>11.1088647441953</v>
       </c>
       <c r="G250" t="n">
         <v>524529176</v>
       </c>
       <c r="H250" t="n">
-        <v>74399216402.95679</v>
+        <v>74934238403.5072</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1073991735399672</v>
+        <v>0.1124932657702152</v>
       </c>
     </row>
   </sheetData>
@@ -7151,75 +7163,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7255,13 +7267,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7297,13 +7309,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7582,7 +7594,7 @@
       <c r="I10" t="n">
         <v>0.3150000000000001</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7595,13 +7607,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7628,7 +7640,7 @@
       <c r="I11" t="n">
         <v>0.3450000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -7641,13 +7653,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7674,7 +7686,7 @@
       <c r="I12" t="n">
         <v>0.7750000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K12" t="n">
@@ -7687,13 +7699,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7720,7 +7732,7 @@
       <c r="I13" t="n">
         <v>1.92</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="K13" t="n">
@@ -7733,13 +7745,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7766,7 +7778,7 @@
       <c r="I14" t="n">
         <v>2.05</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K14" t="n">
@@ -7779,13 +7791,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7812,7 +7824,7 @@
       <c r="I15" t="n">
         <v>2.39</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K15" t="n">
@@ -7825,13 +7837,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7858,7 +7870,7 @@
       <c r="I16" t="n">
         <v>2.575</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K16" t="n">
@@ -7871,13 +7883,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7904,7 +7916,7 @@
       <c r="I17" t="n">
         <v>2.225</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="K17" t="n">
@@ -7917,13 +7929,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7950,7 +7962,7 @@
       <c r="I18" t="n">
         <v>1.055</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K18" t="n">
@@ -7963,13 +7975,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7996,7 +8008,7 @@
       <c r="I19" t="n">
         <v>1.365</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="K19" t="n">
@@ -8009,13 +8021,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8042,7 +8054,7 @@
       <c r="I20" t="n">
         <v>1.84</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K20" t="n">
@@ -8055,13 +8067,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8088,7 +8100,7 @@
       <c r="I21" t="n">
         <v>2.03</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K21" t="n">
@@ -8101,13 +8113,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8134,7 +8146,7 @@
       <c r="I22" t="n">
         <v>4.025</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="K22" t="n">
@@ -8147,13 +8159,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8180,7 +8192,7 @@
       <c r="I23" t="n">
         <v>4.324999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K23" t="n">
@@ -8193,13 +8205,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8226,7 +8238,7 @@
       <c r="I24" t="n">
         <v>4.404999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K24" t="n">
@@ -8239,13 +8251,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8272,7 +8284,7 @@
       <c r="I25" t="n">
         <v>5.57</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K25" t="n">
@@ -8285,13 +8297,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8318,7 +8330,7 @@
       <c r="I26" t="n">
         <v>5.319999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="K26" t="n">
@@ -8331,13 +8343,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8364,7 +8376,7 @@
       <c r="I27" t="n">
         <v>3.799999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K27" t="n">
@@ -8377,13 +8389,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8410,7 +8422,7 @@
       <c r="I28" t="n">
         <v>2.52</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K28" t="n">
@@ -8423,13 +8435,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8456,7 +8468,7 @@
       <c r="I29" t="n">
         <v>-6.959999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K29" t="n">
@@ -8469,13 +8481,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8502,7 +8514,7 @@
       <c r="I30" t="n">
         <v>-8.290000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K30" t="n">
@@ -8515,13 +8527,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8548,7 +8560,7 @@
       <c r="I31" t="n">
         <v>-8.84</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K31" t="n">
@@ -8561,13 +8573,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8594,7 +8606,7 @@
       <c r="I32" t="n">
         <v>-9.379999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K32" t="n">
@@ -8607,13 +8619,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8640,7 +8652,7 @@
       <c r="I33" t="n">
         <v>-2.26</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K33" t="n">
@@ -8653,13 +8665,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8686,7 +8698,7 @@
       <c r="I34" t="n">
         <v>-1.99</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K34" t="n">
@@ -8699,13 +8711,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8732,7 +8744,7 @@
       <c r="I35" t="n">
         <v>-1.08</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="K35" t="n">
@@ -8745,13 +8757,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8778,7 +8790,7 @@
       <c r="I36" t="n">
         <v>-0.51</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K36" t="n">
@@ -8791,13 +8803,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8824,7 +8836,7 @@
       <c r="I37" t="n">
         <v>0.01000000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K37" t="n">
@@ -8837,13 +8849,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8870,7 +8882,7 @@
       <c r="I38" t="n">
         <v>4.46</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K38" t="n">
@@ -8883,13 +8895,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8916,7 +8928,7 @@
       <c r="I39" t="n">
         <v>5.51</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K39" t="n">
@@ -8929,13 +8941,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8962,7 +8974,7 @@
       <c r="I40" t="n">
         <v>6.67</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K40" t="n">
@@ -8975,13 +8987,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9008,7 +9020,7 @@
       <c r="I41" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K41" t="n">
@@ -9021,13 +9033,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9054,7 +9066,7 @@
       <c r="I42" t="n">
         <v>5.89</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K42" t="n">
@@ -9067,13 +9079,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9100,7 +9112,7 @@
       <c r="I43" t="n">
         <v>5.889999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K43" t="n">
@@ -9113,13 +9125,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9146,7 +9158,7 @@
       <c r="I44" t="n">
         <v>6.15</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K44" t="n">
@@ -9159,13 +9171,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9192,7 +9204,7 @@
       <c r="I45" t="n">
         <v>5.16</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K45" t="n">
@@ -9205,13 +9217,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9238,7 +9250,7 @@
       <c r="I46" t="n">
         <v>4.720000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K46" t="n">
@@ -9251,13 +9263,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9284,7 +9296,7 @@
       <c r="I47" t="n">
         <v>3.64</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K47" t="n">
@@ -9297,13 +9309,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9330,7 +9342,7 @@
       <c r="I48" t="n">
         <v>0.6100000000000001</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K48" t="n">
@@ -9343,13 +9355,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9376,7 +9388,7 @@
       <c r="I49" t="n">
         <v>-0.52</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K49" t="n">
@@ -9389,13 +9401,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9422,7 +9434,7 @@
       <c r="I50" t="n">
         <v>-1.04</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K50" t="n">
@@ -9435,13 +9447,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9468,7 +9480,7 @@
       <c r="I51" t="n">
         <v>0.09999999999999987</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K51" t="n">
@@ -9481,13 +9493,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9514,7 +9526,7 @@
       <c r="I52" t="n">
         <v>3.22</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K52" t="n">
@@ -9527,13 +9539,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9560,7 +9572,7 @@
       <c r="I53" t="n">
         <v>5.17</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K53" t="n">
@@ -9573,13 +9585,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9606,7 +9618,7 @@
       <c r="I54" t="n">
         <v>7.99</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K54" t="n">
@@ -9619,13 +9631,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9652,7 +9664,7 @@
       <c r="I55" t="n">
         <v>7.5</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K55" t="n">
@@ -9665,13 +9677,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9698,7 +9710,7 @@
       <c r="I56" t="n">
         <v>9.76</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K56" t="n">
@@ -9711,13 +9723,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9744,7 +9756,7 @@
       <c r="I57" t="n">
         <v>12.74</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K57" t="n">
@@ -9757,13 +9769,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9790,7 +9802,7 @@
       <c r="I58" t="n">
         <v>13.22</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K58" t="n">
@@ -9803,13 +9815,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9836,7 +9848,7 @@
       <c r="I59" t="n">
         <v>16</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K59" t="n">
@@ -9849,13 +9861,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9882,7 +9894,7 @@
       <c r="I60" t="n">
         <v>14.85</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K60" t="n">
@@ -9895,13 +9907,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9928,7 +9940,7 @@
       <c r="I61" t="n">
         <v>13.47</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K61" t="n">
@@ -9941,13 +9953,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9974,7 +9986,7 @@
       <c r="I62" t="n">
         <v>13</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K62" t="n">
@@ -9987,13 +9999,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10020,7 +10032,7 @@
       <c r="I63" t="n">
         <v>12.65</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10033,13 +10045,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10066,7 +10078,7 @@
       <c r="I64" t="n">
         <v>12.94</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K64" t="n">
@@ -10079,13 +10091,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10112,7 +10124,7 @@
       <c r="I65" t="n">
         <v>12.41</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K65" t="n">
@@ -10125,13 +10137,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10158,7 +10170,7 @@
       <c r="I66" t="n">
         <v>11.25</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K66" t="n">
@@ -10171,13 +10183,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10204,7 +10216,7 @@
       <c r="I67" t="n">
         <v>10.8</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K67" t="n">
@@ -10217,13 +10229,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10250,7 +10262,7 @@
       <c r="I68" t="n">
         <v>10.31</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K68" t="n">
@@ -10263,13 +10275,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10296,7 +10308,7 @@
       <c r="I69" t="n">
         <v>10.06</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K69" t="n">
@@ -10309,13 +10321,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10342,7 +10354,7 @@
       <c r="I70" t="n">
         <v>9.120000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K70" t="n">
@@ -10355,13 +10367,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10388,7 +10400,7 @@
       <c r="I71" t="n">
         <v>10.17</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K71" t="n">
@@ -10401,13 +10413,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10434,7 +10446,7 @@
       <c r="I72" t="n">
         <v>12.86</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K72" t="n">
@@ -10471,52 +10483,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C2" t="n">
@@ -10545,10 +10557,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40228</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C3" t="n">
@@ -10577,10 +10589,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40296</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C4" t="n">
@@ -10609,10 +10621,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C5" t="n">
@@ -10641,10 +10653,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40479</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="C6" t="n">
@@ -10673,10 +10685,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C7" t="n">
@@ -10705,10 +10717,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C8" t="n">
@@ -10737,10 +10749,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C9" t="n">
@@ -10769,10 +10781,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40842</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C10" t="n">
@@ -10801,10 +10813,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C11" t="n">
@@ -10833,10 +10845,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C12" t="n">
@@ -10865,10 +10877,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41116</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C13" t="n">
@@ -10897,10 +10909,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="C14" t="n">
@@ -10929,10 +10941,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C15" t="n">
@@ -10961,10 +10973,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="C16" t="n">
@@ -10993,10 +11005,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C17" t="n">
@@ -11025,10 +11037,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="C18" t="n">
@@ -11057,10 +11069,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C19" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41849</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C20" t="n">
@@ -11121,10 +11133,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C21" t="n">
@@ -11153,10 +11165,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42045</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="C22" t="n">
@@ -11185,10 +11197,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C23" t="n">
@@ -11217,10 +11229,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42215</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C24" t="n">
@@ -11249,10 +11261,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42306</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C25" t="n">
@@ -11281,10 +11293,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42418</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C26" t="n">
@@ -11313,10 +11325,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42488</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C27" t="n">
@@ -11345,10 +11357,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42578</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C28" t="n">
@@ -11377,10 +11389,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42669</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C29" t="n">
@@ -11409,10 +11421,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42783</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C30" t="n">
@@ -11441,10 +11453,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="C31" t="n">
@@ -11473,10 +11485,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42941</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C32" t="n">
@@ -11505,10 +11517,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43034</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C33" t="n">
@@ -11537,10 +11549,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43147</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C34" t="n">
@@ -11569,10 +11581,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43216</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C35" t="n">
@@ -11601,10 +11613,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43306</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C36" t="n">
@@ -11633,10 +11645,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C37" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C38" t="n">
@@ -11697,10 +11709,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C39" t="n">
@@ -11729,10 +11741,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C40" t="n">
@@ -11761,10 +11773,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C41" t="n">
@@ -11793,10 +11805,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43874</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C42" t="n">
@@ -11825,10 +11837,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43950</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C43" t="n">
@@ -11857,10 +11869,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44042</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C44" t="n">
@@ -11889,10 +11901,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44133</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C45" t="n">
@@ -11921,10 +11933,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C46" t="n">
@@ -11953,10 +11965,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44315</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C47" t="n">
@@ -11985,10 +11997,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44405</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C48" t="n">
@@ -12017,10 +12029,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44497</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C49" t="n">
@@ -12049,10 +12061,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C50" t="n">
@@ -12081,10 +12093,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44679</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C51" t="n">
@@ -12113,10 +12125,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44770</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C52" t="n">
@@ -12145,10 +12157,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44861</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C53" t="n">
@@ -12177,10 +12189,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C54" t="n">
@@ -12209,10 +12221,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45043</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C55" t="n">
@@ -12241,10 +12253,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45134</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C56" t="n">
@@ -12273,10 +12285,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C57" t="n">
@@ -12305,10 +12317,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C58" t="n">
@@ -12337,10 +12349,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C59" t="n">
@@ -12369,10 +12381,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45498</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C60" t="n">
@@ -12401,10 +12413,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C61" t="n">
@@ -12433,10 +12445,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45701</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C62" t="n">
@@ -12465,10 +12477,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45771</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C63" t="n">
@@ -12497,10 +12509,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C64" t="n">
@@ -12529,10 +12541,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C65" t="n">
@@ -12561,10 +12573,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C66" t="n">
@@ -12593,10 +12605,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46140</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C67" t="n">
@@ -12625,10 +12637,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46231</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C68" t="n">
@@ -12675,12 +12687,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/EOG.xlsx
+++ b/salidas/empresas/EOG.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.69247436523438</v>
+        <v>28.69246482849121</v>
       </c>
       <c r="C2" t="n">
         <v>42.27000045776367</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.87523651123047</v>
+        <v>22.87522506713867</v>
       </c>
       <c r="C3" t="n">
         <v>33.70000076293945</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.43644332885742</v>
+        <v>24.43645477294922</v>
       </c>
       <c r="C4" t="n">
         <v>36</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.85508728027344</v>
+        <v>23.85508918762207</v>
       </c>
       <c r="C5" t="n">
         <v>35.1150016784668</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.30279159545898</v>
+        <v>22.30279350280762</v>
       </c>
       <c r="C6" t="n">
         <v>32.83000183105469</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>23.55278205871582</v>
+        <v>23.55278587341309</v>
       </c>
       <c r="C7" t="n">
         <v>34.66999816894531</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>25.20812606811523</v>
+        <v>25.2081356048584</v>
       </c>
       <c r="C8" t="n">
         <v>37.07500076293945</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>22.11448860168457</v>
+        <v>22.1144847869873</v>
       </c>
       <c r="C10" t="n">
         <v>32.52500152587891</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>22.63894462585449</v>
+        <v>22.63893699645996</v>
       </c>
       <c r="C11" t="n">
         <v>33.26499938964844</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>24.00007057189941</v>
+        <v>24.00007820129395</v>
       </c>
       <c r="C12" t="n">
         <v>35.26499938964844</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>21.2505989074707</v>
+        <v>21.25059509277344</v>
       </c>
       <c r="C13" t="n">
         <v>31.22500038146973</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.54723930358887</v>
+        <v>23.5472412109375</v>
       </c>
       <c r="C14" t="n">
         <v>34.56499862670898</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>23.07378196716309</v>
+        <v>23.07378005981445</v>
       </c>
       <c r="C15" t="n">
         <v>33.86999893188477</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>24.30000877380371</v>
+        <v>24.30001068115234</v>
       </c>
       <c r="C16" t="n">
         <v>35.66999816894531</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.22526359558105</v>
+        <v>26.22525405883789</v>
       </c>
       <c r="C18" t="n">
         <v>38.45000076293945</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.91569519042969</v>
+        <v>24.91570281982422</v>
       </c>
       <c r="C19" t="n">
         <v>36.52999877929688</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>23.93513298034668</v>
+        <v>23.93512535095215</v>
       </c>
       <c r="C20" t="n">
         <v>35.04999923706055</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>24.69655609130859</v>
+        <v>24.69655227661133</v>
       </c>
       <c r="C22" t="n">
         <v>36.16500091552734</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>30.28530693054199</v>
+        <v>30.28532791137695</v>
       </c>
       <c r="C23" t="n">
         <v>44.29999923706055</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>30.50750160217285</v>
+        <v>30.50750923156738</v>
       </c>
       <c r="C25" t="n">
         <v>44.625</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.88007164001465</v>
+        <v>29.88006973266602</v>
       </c>
       <c r="C26" t="n">
         <v>43.66500091552734</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>40.71258544921875</v>
+        <v>40.71258163452148</v>
       </c>
       <c r="C27" t="n">
         <v>59.49499893188477</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>41.05815505981445</v>
+        <v>41.05815124511719</v>
       </c>
       <c r="C28" t="n">
         <v>60</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>44.68634796142578</v>
+        <v>44.68635940551758</v>
       </c>
       <c r="C29" t="n">
         <v>65.23999786376953</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>44.05277252197266</v>
+        <v>44.05277633666992</v>
       </c>
       <c r="C30" t="n">
         <v>64.31500244140625</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>44.93292617797852</v>
+        <v>44.93293762207031</v>
       </c>
       <c r="C31" t="n">
         <v>65.59999847412109</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.46392059326172</v>
+        <v>34.46390151977539</v>
       </c>
       <c r="C32" t="n">
         <v>50.26499938964844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>35.79750061035156</v>
+        <v>35.79748916625977</v>
       </c>
       <c r="C33" t="n">
         <v>52.20999908447266</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>30.66888809204102</v>
+        <v>30.66886520385742</v>
       </c>
       <c r="C34" t="n">
         <v>44.72999954223633</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>27.7940616607666</v>
+        <v>27.7940559387207</v>
       </c>
       <c r="C35" t="n">
         <v>40.45999908447266</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>29.20232009887695</v>
+        <v>29.20232391357422</v>
       </c>
       <c r="C36" t="n">
         <v>42.5099983215332</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.86862945556641</v>
+        <v>22.86862182617188</v>
       </c>
       <c r="C37" t="n">
         <v>33.29000091552734</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>23.32429504394531</v>
+        <v>23.32430267333984</v>
       </c>
       <c r="C38" t="n">
         <v>33.8849983215332</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.22219657897949</v>
+        <v>17.22218894958496</v>
       </c>
       <c r="C39" t="n">
         <v>25.02000045776367</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.84666061401367</v>
+        <v>18.8466682434082</v>
       </c>
       <c r="C40" t="n">
         <v>27.3799991607666</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.89905548095703</v>
+        <v>21.89905166625977</v>
       </c>
       <c r="C41" t="n">
         <v>31.73999977111816</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>25.24877738952637</v>
+        <v>25.24877548217773</v>
       </c>
       <c r="C42" t="n">
         <v>36.59500122070312</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>23.43075180053711</v>
+        <v>23.43074417114258</v>
       </c>
       <c r="C43" t="n">
         <v>33.95999908447266</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.89406967163086</v>
+        <v>24.89406394958496</v>
       </c>
       <c r="C45" t="n">
         <v>36</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>28.87365341186523</v>
+        <v>28.8736572265625</v>
       </c>
       <c r="C46" t="n">
         <v>41.75500106811523</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>28.27977561950684</v>
+        <v>28.2797679901123</v>
       </c>
       <c r="C47" t="n">
         <v>40.83000183105469</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.95246124267578</v>
+        <v>29.95244979858398</v>
       </c>
       <c r="C48" t="n">
         <v>43.24499893188477</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.69609451293945</v>
+        <v>33.69608306884766</v>
       </c>
       <c r="C49" t="n">
         <v>48.65000152587891</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>31.36110496520996</v>
+        <v>31.36111259460449</v>
       </c>
       <c r="C50" t="n">
         <v>45.20999908447266</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>32.62013626098633</v>
+        <v>32.6201171875</v>
       </c>
       <c r="C51" t="n">
         <v>47.02500152587891</v>
@@ -1472,7 +1472,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.23514938354492</v>
+        <v>32.23513793945312</v>
       </c>
       <c r="C52" t="n">
         <v>46.47000122070312</v>
@@ -1497,7 +1497,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.94371032714844</v>
+        <v>38.9437141418457</v>
       </c>
       <c r="C53" t="n">
         <v>56.06000137329102</v>
@@ -1522,7 +1522,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>36.41507339477539</v>
+        <v>36.41508483886719</v>
       </c>
       <c r="C54" t="n">
         <v>52.41999816894531</v>
@@ -1547,7 +1547,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>34.16778945922852</v>
+        <v>34.16780090332031</v>
       </c>
       <c r="C55" t="n">
         <v>49.18500137329102</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>33.91481781005859</v>
+        <v>33.91482162475586</v>
       </c>
       <c r="C56" t="n">
         <v>48.75</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>30.21723937988281</v>
+        <v>30.21724319458008</v>
       </c>
       <c r="C57" t="n">
         <v>43.43500137329102</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>32.3390998840332</v>
+        <v>32.33910369873047</v>
       </c>
       <c r="C58" t="n">
         <v>46.48500061035156</v>
@@ -1647,7 +1647,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.34792709350586</v>
+        <v>33.34791946411133</v>
       </c>
       <c r="C59" t="n">
         <v>47.86000061035156</v>
@@ -1672,7 +1672,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>30.98931503295898</v>
+        <v>30.98932075500488</v>
       </c>
       <c r="C60" t="n">
         <v>44.47499847412109</v>
@@ -1697,7 +1697,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>31.84634971618652</v>
+        <v>31.84636116027832</v>
       </c>
       <c r="C61" t="n">
         <v>45.70500183105469</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>37.1247444152832</v>
+        <v>37.12472915649414</v>
       </c>
       <c r="C62" t="n">
         <v>53.19499969482422</v>
@@ -1747,7 +1747,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.19051742553711</v>
+        <v>39.19053268432617</v>
       </c>
       <c r="C63" t="n">
         <v>56.15499877929688</v>
@@ -1776,7 +1776,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>41.35400390625</v>
+        <v>41.35399627685547</v>
       </c>
       <c r="C64" t="n">
         <v>59.25500106811523</v>
@@ -1805,7 +1805,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.5066032409668</v>
+        <v>39.50661468505859</v>
       </c>
       <c r="C65" t="n">
         <v>56.52500152587891</v>
@@ -1834,7 +1834,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.14021301269531</v>
+        <v>38.14020919799805</v>
       </c>
       <c r="C66" t="n">
         <v>54.56999969482422</v>
@@ -1863,7 +1863,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>36.53619003295898</v>
+        <v>36.53620147705078</v>
       </c>
       <c r="C67" t="n">
         <v>52.27500152587891</v>
@@ -1892,7 +1892,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>35.70281219482422</v>
+        <v>35.70283126831055</v>
       </c>
       <c r="C68" t="n">
         <v>51</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>32.40907287597656</v>
+        <v>32.40907669067383</v>
       </c>
       <c r="C69" t="n">
         <v>46.29499816894531</v>
@@ -1950,7 +1950,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>24.8554744720459</v>
+        <v>24.85547065734863</v>
       </c>
       <c r="C70" t="n">
         <v>35.50500106811523</v>
@@ -1979,7 +1979,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>31.36498260498047</v>
+        <v>31.3649845123291</v>
       </c>
       <c r="C71" t="n">
         <v>44.71500015258789</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>36.3837776184082</v>
+        <v>36.38379669189453</v>
       </c>
       <c r="C72" t="n">
         <v>51.86999893188477</v>
@@ -2037,7 +2037,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>34.54952239990234</v>
+        <v>34.54951858520508</v>
       </c>
       <c r="C73" t="n">
         <v>49.25500106811523</v>
@@ -2066,7 +2066,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>37.28334045410156</v>
+        <v>37.28334426879883</v>
       </c>
       <c r="C74" t="n">
         <v>53.06999969482422</v>
@@ -2095,7 +2095,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>39.9951171875</v>
+        <v>39.99510955810547</v>
       </c>
       <c r="C75" t="n">
         <v>56.93000030517578</v>
@@ -2124,7 +2124,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>39.02560806274414</v>
+        <v>39.02561950683594</v>
       </c>
       <c r="C76" t="n">
         <v>55.54999923706055</v>
@@ -2153,7 +2153,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>38.63628768920898</v>
+        <v>38.63629150390625</v>
       </c>
       <c r="C77" t="n">
         <v>54.90499877929688</v>
@@ -2182,7 +2182,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>34.93838500976562</v>
+        <v>34.93837356567383</v>
       </c>
       <c r="C78" t="n">
         <v>49.65000152587891</v>
@@ -2211,7 +2211,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>31.70489883422852</v>
+        <v>31.70492172241211</v>
       </c>
       <c r="C79" t="n">
         <v>45.05500030517578</v>
@@ -2240,7 +2240,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>34.54900360107422</v>
+        <v>34.54899978637695</v>
       </c>
       <c r="C80" t="n">
         <v>49.00500106811523</v>
@@ -2269,7 +2269,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>38.17627334594727</v>
+        <v>38.17628860473633</v>
       </c>
       <c r="C81" t="n">
         <v>54.15000152587891</v>
@@ -2298,7 +2298,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>39.4981689453125</v>
+        <v>39.4981803894043</v>
       </c>
       <c r="C82" t="n">
         <v>56.02500152587891</v>
@@ -2327,7 +2327,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>41.1275634765625</v>
+        <v>41.12755584716797</v>
       </c>
       <c r="C83" t="n">
         <v>58.24499893188477</v>
@@ -2356,7 +2356,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>41.52651214599609</v>
+        <v>41.52650833129883</v>
       </c>
       <c r="C84" t="n">
         <v>58.81000137329102</v>
@@ -2385,7 +2385,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.64572143554688</v>
+        <v>42.64569854736328</v>
       </c>
       <c r="C85" t="n">
         <v>60.39500045776367</v>
@@ -2414,7 +2414,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>44.18526077270508</v>
+        <v>44.18527603149414</v>
       </c>
       <c r="C86" t="n">
         <v>62.4900016784668</v>
@@ -2472,7 +2472,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>45.27771759033203</v>
+        <v>45.2777099609375</v>
       </c>
       <c r="C88" t="n">
         <v>64.03500366210938</v>
@@ -2501,7 +2501,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.89761734008789</v>
+        <v>42.89764022827148</v>
       </c>
       <c r="C89" t="n">
         <v>60.58000183105469</v>
@@ -2530,7 +2530,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>45.70885467529297</v>
+        <v>45.70885848999023</v>
       </c>
       <c r="C90" t="n">
         <v>64.55000305175781</v>
@@ -2559,7 +2559,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>46.622314453125</v>
+        <v>46.62230682373047</v>
       </c>
       <c r="C91" t="n">
         <v>65.83999633789062</v>
@@ -2588,7 +2588,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>51.57887268066406</v>
+        <v>51.57886505126953</v>
       </c>
       <c r="C92" t="n">
         <v>72.74500274658203</v>
@@ -2617,7 +2617,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>55.67710876464844</v>
+        <v>55.67710113525391</v>
       </c>
       <c r="C93" t="n">
         <v>78.52500152587891</v>
@@ -2646,7 +2646,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>60.01288223266602</v>
+        <v>60.01286315917969</v>
       </c>
       <c r="C94" t="n">
         <v>84.63999938964844</v>
@@ -2675,7 +2675,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>63.31178665161133</v>
+        <v>63.31180191040039</v>
       </c>
       <c r="C95" t="n">
         <v>89.19999694824219</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>58.55631637573242</v>
+        <v>58.55631256103516</v>
       </c>
       <c r="C96" t="n">
         <v>82.5</v>
@@ -2733,7 +2733,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>59.564208984375</v>
+        <v>59.56418991088867</v>
       </c>
       <c r="C97" t="n">
         <v>83.91999816894531</v>
@@ -2820,7 +2820,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>69.69583129882812</v>
+        <v>69.69583892822266</v>
       </c>
       <c r="C100" t="n">
         <v>98.08499908447266</v>
@@ -2849,7 +2849,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>69.72384643554688</v>
+        <v>69.72381591796875</v>
       </c>
       <c r="C101" t="n">
         <v>98</v>
@@ -2878,7 +2878,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>75.27323150634766</v>
+        <v>75.27326965332031</v>
       </c>
       <c r="C102" t="n">
         <v>105.8000030517578</v>
@@ -2907,7 +2907,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>83.14208221435547</v>
+        <v>83.14208984375</v>
       </c>
       <c r="C103" t="n">
         <v>116.8600006103516</v>
@@ -2936,7 +2936,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>77.94725036621094</v>
+        <v>77.94721984863281</v>
       </c>
       <c r="C104" t="n">
         <v>109.4400024414062</v>
@@ -2965,7 +2965,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>78.26058959960938</v>
+        <v>78.26060485839844</v>
       </c>
       <c r="C105" t="n">
         <v>109.879997253418</v>
@@ -2994,7 +2994,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.52570343017578</v>
+        <v>70.52571105957031</v>
       </c>
       <c r="C106" t="n">
         <v>99.01999664306641</v>
@@ -3052,7 +3052,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>61.88919830322266</v>
+        <v>61.88920593261719</v>
       </c>
       <c r="C108" t="n">
         <v>86.72000122070312</v>
@@ -3081,7 +3081,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>65.70736694335938</v>
+        <v>65.70735168457031</v>
       </c>
       <c r="C109" t="n">
         <v>92.06999969482422</v>
@@ -3110,7 +3110,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>63.66349411010742</v>
+        <v>63.66350173950195</v>
       </c>
       <c r="C110" t="n">
         <v>89.02999877929688</v>
@@ -3139,7 +3139,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>64.15692901611328</v>
+        <v>64.15694427490234</v>
       </c>
       <c r="C111" t="n">
         <v>89.72000122070312</v>
@@ -3168,7 +3168,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>65.56561279296875</v>
+        <v>65.56562805175781</v>
       </c>
       <c r="C112" t="n">
         <v>91.69000244140625</v>
@@ -3197,7 +3197,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>70.88288116455078</v>
+        <v>70.88285064697266</v>
       </c>
       <c r="C113" t="n">
         <v>98.94999694824219</v>
@@ -3226,7 +3226,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>63.53313446044922</v>
+        <v>63.53312301635742</v>
       </c>
       <c r="C114" t="n">
         <v>88.69000244140625</v>
@@ -3284,7 +3284,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>55.4043083190918</v>
+        <v>55.404296875</v>
       </c>
       <c r="C116" t="n">
         <v>77.19000244140625</v>
@@ -3313,7 +3313,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>56.20817947387695</v>
+        <v>56.20820617675781</v>
       </c>
       <c r="C117" t="n">
         <v>78.30999755859375</v>
@@ -3342,7 +3342,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>52.2533073425293</v>
+        <v>52.25332641601562</v>
       </c>
       <c r="C118" t="n">
         <v>72.80000305175781</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>61.74177169799805</v>
+        <v>61.74179077148438</v>
       </c>
       <c r="C119" t="n">
         <v>85.84999847412109</v>
@@ -3400,7 +3400,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>60.00134658813477</v>
+        <v>60.00138092041016</v>
       </c>
       <c r="C120" t="n">
         <v>83.43000030517578</v>
@@ -3454,7 +3454,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>51.21305084228516</v>
+        <v>51.21305465698242</v>
       </c>
       <c r="C122" t="n">
         <v>71.01999664306641</v>
@@ -3508,7 +3508,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>52.33797836303711</v>
+        <v>52.33797454833984</v>
       </c>
       <c r="C124" t="n">
         <v>72.58000183105469</v>
@@ -3535,7 +3535,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>59.70731353759766</v>
+        <v>59.70732116699219</v>
       </c>
       <c r="C125" t="n">
         <v>82.62000274658203</v>
@@ -3562,7 +3562,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>58.79672241210938</v>
+        <v>58.79673385620117</v>
       </c>
       <c r="C126" t="n">
         <v>81.36000061035156</v>
@@ -3589,7 +3589,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.28545379638672</v>
+        <v>60.28543853759766</v>
       </c>
       <c r="C127" t="n">
         <v>83.41999816894531</v>
@@ -3616,7 +3616,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>59.15918350219727</v>
+        <v>59.15917587280273</v>
       </c>
       <c r="C128" t="n">
         <v>81.69999694824219</v>
@@ -3643,7 +3643,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>64.07582855224609</v>
+        <v>64.07585144042969</v>
       </c>
       <c r="C129" t="n">
         <v>88.48999786376953</v>
@@ -3670,7 +3670,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>70.02797698974609</v>
+        <v>70.0279541015625</v>
       </c>
       <c r="C130" t="n">
         <v>96.70999908447266</v>
@@ -3751,7 +3751,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>73.334716796875</v>
+        <v>73.33474731445312</v>
       </c>
       <c r="C133" t="n">
         <v>101.0999984741211</v>
@@ -3805,7 +3805,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.46629333496094</v>
+        <v>70.46625518798828</v>
       </c>
       <c r="C135" t="n">
         <v>96.98999786376953</v>
@@ -3832,7 +3832,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>70.87313079833984</v>
+        <v>70.87311553955078</v>
       </c>
       <c r="C136" t="n">
         <v>97.55000305175781</v>
@@ -3859,7 +3859,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>67.31888580322266</v>
+        <v>67.31889343261719</v>
       </c>
       <c r="C137" t="n">
         <v>92.5</v>
@@ -3886,7 +3886,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>65.72506713867188</v>
+        <v>65.72505187988281</v>
       </c>
       <c r="C138" t="n">
         <v>90.30999755859375</v>
@@ -3913,7 +3913,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>65.87789916992188</v>
+        <v>65.87790679931641</v>
       </c>
       <c r="C139" t="n">
         <v>90.51999664306641</v>
@@ -3967,7 +3967,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>61.96826171875</v>
+        <v>61.96826553344727</v>
       </c>
       <c r="C141" t="n">
         <v>84.98999786376953</v>
@@ -3994,7 +3994,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>70.53546142578125</v>
+        <v>70.53546905517578</v>
       </c>
       <c r="C142" t="n">
         <v>96.73999786376953</v>
@@ -4021,7 +4021,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>72.9444580078125</v>
+        <v>72.94446563720703</v>
       </c>
       <c r="C143" t="n">
         <v>99.87000274658203</v>
@@ -4048,7 +4048,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>74.73393249511719</v>
+        <v>74.73396301269531</v>
       </c>
       <c r="C144" t="n">
         <v>102.3199996948242</v>
@@ -4077,7 +4077,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.81684112548828</v>
+        <v>78.81684875488281</v>
       </c>
       <c r="C145" t="n">
         <v>107.9100036621094</v>
@@ -4135,7 +4135,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>74.18430328369141</v>
+        <v>74.18429565429688</v>
       </c>
       <c r="C147" t="n">
         <v>101.4199981689453</v>
@@ -4193,7 +4193,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>86.58183288574219</v>
+        <v>86.58181762695312</v>
       </c>
       <c r="C149" t="n">
         <v>118.1699981689453</v>
@@ -4222,7 +4222,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>86.31807708740234</v>
+        <v>86.31806182861328</v>
       </c>
       <c r="C150" t="n">
         <v>117.8099975585938</v>
@@ -4251,7 +4251,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>91.16844177246094</v>
+        <v>91.16844940185547</v>
       </c>
       <c r="C151" t="n">
         <v>124.4300003051758</v>
@@ -4280,7 +4280,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>94.61185455322266</v>
+        <v>94.61183929443359</v>
       </c>
       <c r="C152" t="n">
         <v>128.9400024414062</v>
@@ -4309,7 +4309,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.75320434570312</v>
+        <v>86.75322723388672</v>
       </c>
       <c r="C153" t="n">
         <v>118.2300033569336</v>
@@ -4338,7 +4338,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>93.60659790039062</v>
+        <v>93.60658264160156</v>
       </c>
       <c r="C154" t="n">
         <v>127.5699996948242</v>
@@ -4367,7 +4367,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>77.43394470214844</v>
+        <v>77.43393707275391</v>
       </c>
       <c r="C155" t="n">
         <v>105.3399963378906</v>
@@ -4396,7 +4396,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>75.94171905517578</v>
+        <v>75.94172668457031</v>
       </c>
       <c r="C156" t="n">
         <v>103.3099975585938</v>
@@ -4483,7 +4483,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>69.25260162353516</v>
+        <v>69.25261688232422</v>
       </c>
       <c r="C159" t="n">
         <v>94</v>
@@ -4512,7 +4512,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>70.12195587158203</v>
+        <v>70.1219482421875</v>
       </c>
       <c r="C160" t="n">
         <v>95.18000030517578</v>
@@ -4570,7 +4570,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>60.44973754882812</v>
+        <v>60.44971084594727</v>
       </c>
       <c r="C162" t="n">
         <v>81.87999725341797</v>
@@ -4599,7 +4599,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>68.77745056152344</v>
+        <v>68.77743530273438</v>
       </c>
       <c r="C163" t="n">
         <v>93.16000366210938</v>
@@ -4628,7 +4628,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>63.58700180053711</v>
+        <v>63.58700942993164</v>
       </c>
       <c r="C164" t="n">
         <v>85.84999847412109</v>
@@ -4657,7 +4657,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>54.95073318481445</v>
+        <v>54.95072174072266</v>
       </c>
       <c r="C165" t="n">
         <v>74.19000244140625</v>
@@ -4686,7 +4686,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>54.97293853759766</v>
+        <v>54.97294998168945</v>
       </c>
       <c r="C166" t="n">
         <v>74.22000122070312</v>
@@ -4715,7 +4715,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>51.55062103271484</v>
+        <v>51.55061340332031</v>
       </c>
       <c r="C167" t="n">
         <v>69.30999755859375</v>
@@ -4744,7 +4744,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>52.73322677612305</v>
+        <v>52.73320770263672</v>
       </c>
       <c r="C168" t="n">
         <v>70.90000152587891</v>
@@ -4773,7 +4773,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>62.2980842590332</v>
+        <v>62.298095703125</v>
       </c>
       <c r="C169" t="n">
         <v>83.76000213623047</v>
@@ -4802,7 +4802,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.40883255004883</v>
+        <v>54.40885162353516</v>
       </c>
       <c r="C170" t="n">
         <v>72.91000366210938</v>
@@ -4860,7 +4860,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>26.80517959594727</v>
+        <v>26.80517387390137</v>
       </c>
       <c r="C172" t="n">
         <v>35.91999816894531</v>
@@ -4889,7 +4889,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>35.77183532714844</v>
+        <v>35.77182388305664</v>
       </c>
       <c r="C173" t="n">
         <v>47.5099983215332</v>
@@ -4918,7 +4918,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.37697601318359</v>
+        <v>38.37698745727539</v>
       </c>
       <c r="C174" t="n">
         <v>50.97000122070312</v>
@@ -4947,7 +4947,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>38.14356994628906</v>
+        <v>38.14357376098633</v>
       </c>
       <c r="C175" t="n">
         <v>50.65999984741211</v>
@@ -4976,7 +4976,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>35.55582809448242</v>
+        <v>35.55583190917969</v>
       </c>
       <c r="C176" t="n">
         <v>46.84999847412109</v>
@@ -5005,7 +5005,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>34.40984725952148</v>
+        <v>34.40985870361328</v>
       </c>
       <c r="C177" t="n">
         <v>45.34000015258789</v>
@@ -5034,7 +5034,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>27.27591896057129</v>
+        <v>27.27591705322266</v>
       </c>
       <c r="C178" t="n">
         <v>35.93999862670898</v>
@@ -5063,7 +5063,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>26.24737548828125</v>
+        <v>26.24737167358398</v>
       </c>
       <c r="C179" t="n">
         <v>34.2400016784668</v>
@@ -5092,7 +5092,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>35.93682861328125</v>
+        <v>35.93682479858398</v>
       </c>
       <c r="C180" t="n">
         <v>46.88000106811523</v>
@@ -5119,7 +5119,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>38.2288703918457</v>
+        <v>38.22887420654297</v>
       </c>
       <c r="C181" t="n">
         <v>49.86999893188477</v>
@@ -5146,7 +5146,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>39.30820465087891</v>
+        <v>39.30818939208984</v>
       </c>
       <c r="C182" t="n">
         <v>50.95999908447266</v>
@@ -5173,7 +5173,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>49.79861068725586</v>
+        <v>49.79861450195312</v>
       </c>
       <c r="C183" t="n">
         <v>64.55999755859375</v>
@@ -5227,7 +5227,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>57.12077331542969</v>
+        <v>57.12078475952148</v>
       </c>
       <c r="C185" t="n">
         <v>73.63999938964844</v>
@@ -5283,7 +5283,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>64.72241973876953</v>
+        <v>64.722412109375</v>
       </c>
       <c r="C187" t="n">
         <v>83.44000244140625</v>
@@ -5312,7 +5312,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>57.53632736206055</v>
+        <v>57.53633499145508</v>
       </c>
       <c r="C188" t="n">
         <v>72.86000061035156</v>
@@ -5341,7 +5341,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>53.31941223144531</v>
+        <v>53.31941986083984</v>
       </c>
       <c r="C189" t="n">
         <v>67.51999664306641</v>
@@ -5399,7 +5399,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>73.34921264648438</v>
+        <v>73.34919738769531</v>
       </c>
       <c r="C191" t="n">
         <v>92.45999908447266</v>
@@ -5428,7 +5428,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>69.0177001953125</v>
+        <v>69.01773834228516</v>
       </c>
       <c r="C192" t="n">
         <v>87</v>
@@ -5457,7 +5457,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>72.10775756835938</v>
+        <v>72.10774993896484</v>
       </c>
       <c r="C193" t="n">
         <v>88.83000183105469</v>
@@ -5486,7 +5486,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>91.15914154052734</v>
+        <v>91.15912628173828</v>
       </c>
       <c r="C194" t="n">
         <v>111.4800033569336</v>
@@ -5515,7 +5515,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>93.97209167480469</v>
+        <v>93.97209930419922</v>
       </c>
       <c r="C195" t="n">
         <v>114.9199981689453</v>
@@ -5544,7 +5544,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>98.33927154541016</v>
+        <v>98.33924865722656</v>
       </c>
       <c r="C196" t="n">
         <v>119.2300033569336</v>
@@ -5573,7 +5573,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>96.88535308837891</v>
+        <v>96.88536071777344</v>
       </c>
       <c r="C197" t="n">
         <v>116.7600021362305</v>
@@ -5602,7 +5602,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>113.64697265625</v>
+        <v>113.6469421386719</v>
       </c>
       <c r="C198" t="n">
         <v>136.9600067138672</v>
@@ -5631,7 +5631,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>92.90100860595703</v>
+        <v>92.9010009765625</v>
       </c>
       <c r="C199" t="n">
         <v>110.4400024414062</v>
@@ -5660,7 +5660,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>94.26848602294922</v>
+        <v>94.26849365234375</v>
       </c>
       <c r="C200" t="n">
         <v>111.2200012207031</v>
@@ -5689,7 +5689,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>102.8121337890625</v>
+        <v>102.8121490478516</v>
       </c>
       <c r="C201" t="n">
         <v>121.3000030517578</v>
@@ -5718,7 +5718,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>95.87075805664062</v>
+        <v>95.87076568603516</v>
       </c>
       <c r="C202" t="n">
         <v>111.7300033569336</v>
@@ -5747,7 +5747,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>117.8360443115234</v>
+        <v>117.8360366821289</v>
       </c>
       <c r="C203" t="n">
         <v>136.5200042724609</v>
@@ -5776,7 +5776,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>122.5055999755859</v>
+        <v>122.5056076049805</v>
       </c>
       <c r="C204" t="n">
         <v>141.9299926757812</v>
@@ -5805,7 +5805,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>113.1253356933594</v>
+        <v>113.1253433227539</v>
       </c>
       <c r="C205" t="n">
         <v>129.5200042724609</v>
@@ -5834,7 +5834,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>116.2449493408203</v>
+        <v>116.2449569702148</v>
       </c>
       <c r="C206" t="n">
         <v>132.25</v>
@@ -5863,7 +5863,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>99.34218597412109</v>
+        <v>99.34219360351562</v>
       </c>
       <c r="C207" t="n">
         <v>113.0199966430664</v>
@@ -5921,7 +5921,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>106.7018508911133</v>
+        <v>106.7018661499023</v>
       </c>
       <c r="C209" t="n">
         <v>119.4700012207031</v>
@@ -5950,7 +5950,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>95.82357788085938</v>
+        <v>95.82357025146484</v>
       </c>
       <c r="C210" t="n">
         <v>107.2900009155273</v>
@@ -6008,7 +6008,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>119.1681976318359</v>
+        <v>119.1681747436523</v>
       </c>
       <c r="C212" t="n">
         <v>132.5299987792969</v>
@@ -6037,7 +6037,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>115.6524047851562</v>
+        <v>115.6523971557617</v>
       </c>
       <c r="C213" t="n">
         <v>128.6199951171875</v>
@@ -6066,7 +6066,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>113.9799499511719</v>
+        <v>113.9799346923828</v>
       </c>
       <c r="C214" t="n">
         <v>126.7600021362305</v>
@@ -6182,7 +6182,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>105.0964279174805</v>
+        <v>105.0964202880859</v>
       </c>
       <c r="C218" t="n">
         <v>113.7900009155273</v>
@@ -6211,7 +6211,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>105.7152252197266</v>
+        <v>105.7152328491211</v>
       </c>
       <c r="C219" t="n">
         <v>114.4599990844727</v>
@@ -6240,7 +6240,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>118.0729904174805</v>
+        <v>118.072998046875</v>
       </c>
       <c r="C220" t="n">
         <v>127.8399963378906</v>
@@ -6269,7 +6269,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>122.8616561889648</v>
+        <v>122.8616485595703</v>
       </c>
       <c r="C221" t="n">
         <v>132.1300048828125</v>
@@ -6298,7 +6298,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>115.8133697509766</v>
+        <v>115.8133544921875</v>
       </c>
       <c r="C222" t="n">
         <v>124.5500030517578</v>
@@ -6327,7 +6327,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>117.0407562255859</v>
+        <v>117.0407485961914</v>
       </c>
       <c r="C223" t="n">
         <v>125.870002746582</v>
@@ -6356,7 +6356,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>118.7270050048828</v>
+        <v>118.7269973754883</v>
       </c>
       <c r="C224" t="n">
         <v>126.8000030517578</v>
@@ -6385,7 +6385,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>120.6184158325195</v>
+        <v>120.6184005737305</v>
       </c>
       <c r="C225" t="n">
         <v>128.8200073242188</v>
@@ -6414,7 +6414,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>115.103401184082</v>
+        <v>115.1034088134766</v>
       </c>
       <c r="C226" t="n">
         <v>122.9300003051758</v>
@@ -6443,7 +6443,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>115.016960144043</v>
+        <v>115.0169677734375</v>
       </c>
       <c r="C227" t="n">
         <v>121.9599990844727</v>
@@ -6472,7 +6472,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>125.6736755371094</v>
+        <v>125.6736526489258</v>
       </c>
       <c r="C228" t="n">
         <v>133.2599945068359</v>
@@ -6501,7 +6501,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>115.6016693115234</v>
+        <v>115.6016616821289</v>
       </c>
       <c r="C229" t="n">
         <v>122.5800018310547</v>
@@ -6530,7 +6530,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>119.4727249145508</v>
+        <v>119.4727172851562</v>
       </c>
       <c r="C230" t="n">
         <v>125.7900009155273</v>
@@ -6675,7 +6675,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>114.64306640625</v>
+        <v>114.6430740356445</v>
       </c>
       <c r="C235" t="n">
         <v>119.6100006103516</v>
@@ -6704,7 +6704,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>115.9879531860352</v>
+        <v>115.9879608154297</v>
       </c>
       <c r="C236" t="n">
         <v>120.0199966430664</v>
@@ -6791,7 +6791,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>103.2664566040039</v>
+        <v>103.2664489746094</v>
       </c>
       <c r="C239" t="n">
         <v>105.8399963378906</v>
